--- a/property_management_forms/022_estate_management_form--property_management_forms.xlsx
+++ b/property_management_forms/022_estate_management_form--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'maintenance_request',_'label':_'maintenance',_'value':_1}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'maintenance_request', 'label': 'Maintenance', 'value': 1}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance_request',_'label':_'maintenance',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'maintenance_request', 'label': 'Maintenance', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'maintenance_request',_'label':_'maintenance',_'value':_1}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'maintenance_request', 'label': 'Maintenance', 'value': 1}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance_request',_'label':_'maintenance',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'maintenance_request', 'label': 'Maintenance', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'maintenance_type',_'label':_'maintenance',_'value':_1}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'maintenance_type', 'label': 'Maintenance', 'value': 1}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance_type',_'label':_'maintenance_request',_'value':_2}</t>
+          <t>maintenance_request</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'maintenance_type', 'label': 'maintenance_request', 'value': 2}</t>
+          <t>maintenance request</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maintenance_type',_'label':_'maintenance_type',_'value':_3}</t>
+          <t>maintenance_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maintenance_type', 'label': 'maintenance_type', 'value': 3}</t>
+          <t>maintenance type</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'maintenance_status',_'label':_'pending',_'value':_1}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'maintenance_status', 'label': 'Pending', 'value': 1}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'maintenance_status',_'label':_'in_progress',_'value':_2}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'maintenance_status', 'label': 'In Progress', 'value': 2}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maintenance_status',_'label':_'completed',_'value':_3}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maintenance_status', 'label': 'Completed', 'value': 3}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'priority',_'label':_'high',_'value':_1}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'priority', 'label': 'High', 'value': 1}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'priority',_'label':_'medium',_'value':_2}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'priority', 'label': 'Medium', 'value': 2}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'priority',_'label':_'low',_'value':_3}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'priority', 'label': 'Low', 'value': 3}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'assigned_user',_'label':_'chatjimmy',_'value':_1}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'assigned_user', 'label': 'ChatJimmy', 'value': 1}</t>
+          <t>ChatJimmy</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'assigned_tool',_'label':_'chatjimmy',_'value':_1}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'assigned_tool', 'label': 'chatjimmy', 'value': 1}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'status',_'label':_'pending',_'value':_1}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'status', 'label': 'Pending', 'value': 1}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress',_'label':_'in_progress',_'value':_2}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Progress', 'label': 'In Progress', 'value': 2}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed',_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Completed', 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'completed',_'label':_'done',_'value':_1}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'completed', 'label': 'Done', 'value': 1}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'completed',_'label':_'not_done',_'value':_2}</t>
+          <t>not_done</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'completed', 'label': 'Not Done', 'value': 2}</t>
+          <t>Not Done</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed',_'label':_'in_progress',_'value':_3}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'completed', 'label': 'In Progress', 'value': 3}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
